--- a/product_selector_out/STM32F334.xlsx
+++ b/product_selector_out/STM32F334.xlsx
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>10, 9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>15, 18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr">
@@ -4293,14 +4293,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -4323,9 +4323,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -4378,9 +4378,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
@@ -4620,14 +4620,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -4650,9 +4650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -4705,9 +4705,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
@@ -4947,14 +4947,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -4977,9 +4977,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -5032,9 +5032,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
@@ -5274,14 +5274,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -5304,9 +5304,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -5359,9 +5359,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM15" s="9" t="inlineStr">
@@ -5601,14 +5601,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -5631,9 +5631,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -5686,9 +5686,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM16" s="9" t="inlineStr">
@@ -5928,14 +5928,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -5958,9 +5958,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -6013,9 +6013,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
@@ -6255,14 +6255,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -6285,9 +6285,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="6" t="inlineStr">
@@ -6340,9 +6340,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM18" s="9" t="inlineStr">
@@ -6582,14 +6582,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -6612,9 +6612,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="6" t="inlineStr">
@@ -6667,9 +6667,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AM19" s="9" t="inlineStr">
@@ -6823,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6938,19 +6938,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334C6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7026,19 +7026,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7114,19 +7114,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7136,19 +7136,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7158,19 +7158,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334K8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7202,19 +7202,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7224,19 +7224,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7253,12 +7253,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7268,14 +7268,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7312,14 +7312,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7341,7 +7341,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7363,12 +7363,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334R8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7378,19 +7378,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7400,19 +7400,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7422,19 +7422,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7451,12 +7451,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F334C4</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7466,19 +7466,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7488,19 +7488,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334R8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7510,19 +7510,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F334C8</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7532,27 +7532,203 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>STM32F334C4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32F334C4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32F334C4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32F334C4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>STM32F334C8</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32F334C8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32F334C8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32F334C8</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32F334C8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32F334.xlsx
+++ b/product_selector_out/STM32F334.xlsx
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1753,214 +1753,214 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
+          <t>10, 9</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>24, 25</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AV14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AW14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX14" s="4" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AY14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ14" s="4" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="BA14" s="4" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="BB14" s="4" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="BC14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BD14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BE14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BG14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BH14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BI14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BJ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AS14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AU14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AV14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AX14" s="4" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AY14" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ14" s="4" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="BA14" s="4" t="inlineStr">
-        <is>
-          <t>-40</t>
-        </is>
-      </c>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BI14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BJ14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BK14" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="BL14" s="4" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4535,19 +4535,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -4605,14 +4605,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4620,14 +4620,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -4650,9 +4650,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -4665,9 +4665,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE13" s="9" t="inlineStr">
@@ -4680,14 +4680,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI13" s="9" t="inlineStr">
@@ -4695,9 +4695,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK13" s="9" t="inlineStr">
@@ -4705,9 +4705,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
@@ -4780,14 +4780,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC13" s="9" t="inlineStr">
@@ -4840,9 +4840,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4862,19 +4862,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -4932,14 +4932,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4947,14 +4947,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -4977,9 +4977,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -4992,9 +4992,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE14" s="9" t="inlineStr">
@@ -5007,14 +5007,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI14" s="9" t="inlineStr">
@@ -5022,9 +5022,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK14" s="9" t="inlineStr">
@@ -5032,9 +5032,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
@@ -5107,14 +5107,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC14" s="9" t="inlineStr">
@@ -5167,9 +5167,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5843,19 +5843,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -5913,14 +5913,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -5928,14 +5928,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -5958,9 +5958,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -5973,9 +5973,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE17" s="9" t="inlineStr">
@@ -5988,14 +5988,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AH17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AG17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AI17" s="9" t="inlineStr">
@@ -6003,9 +6003,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AJ17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AK17" s="9" t="inlineStr">
@@ -6013,9 +6013,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
@@ -6088,14 +6088,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC17" s="9" t="inlineStr">
@@ -6148,9 +6148,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6967,7 +6967,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6982,14 +6982,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7033,7 +7033,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7048,14 +7048,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F334K6</t>
+          <t>STM32F334R6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7121,7 +7121,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7143,7 +7143,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7165,7 +7165,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F334K8</t>
+          <t>STM32F334K4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7187,7 +7187,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7231,7 +7231,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7253,7 +7253,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7275,7 +7275,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F334R6</t>
+          <t>STM32F334C4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7312,14 +7312,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7341,7 +7341,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7363,7 +7363,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7378,14 +7378,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>summary row reads USART = 2 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
+          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F334K4</t>
+          <t>STM32F334C8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7399,336 +7399,6 @@
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32F334R8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32F334C4</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F334x4/6/8 family device features and peripheral counts (continued) lists LQFP48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>summary row reads USART = 3 with no UART split; ST publishes USART and UART separately, so the cell's combined count answers neither column</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32F334C8</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
         <is>
           <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32F334.xlsx
+++ b/product_selector_out/STM32F334.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -1644,6 +1656,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1971,6 +1988,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -2952,6 +2984,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
@@ -3603,12 +3645,17 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f334c4.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3629,16 +3676,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3651,6 +3696,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3670,7 +3716,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3695,7 +3743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3763,6 +3811,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4096,6 +4145,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4191,6 +4245,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4513,7 +4568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4845,6 +4905,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5172,6 +5237,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -5494,7 +5564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5821,7 +5896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6153,6 +6233,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6475,7 +6560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6802,7 +6892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6810,8 +6905,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
